--- a/Analysis/Prompt_Ablation/prompt_ablation_summary_by_decision_type.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_summary_by_decision_type.xlsx
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5154412297852095</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="5">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.646361486186504</v>
+        <v>0.6685185185185185</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6888888888888889</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9277777777777778</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2844368850782693</v>
+        <v>0.3074074074074074</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6715391120055141</v>
+        <v>0.6925925925925926</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6777777777777778</v>
+        <v>0.6722222222222223</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9277777777777778</v>
       </c>
     </row>
     <row r="14">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.673578038884095</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6722222222222223</v>
       </c>
       <c r="G16" t="n">
-        <v>0.95</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-0.005128205128205138</v>
+        <v>-0.005128205128205132</v>
       </c>
       <c r="F17" t="n">
         <v>0.282051282051282</v>
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.6941354842811942</v>
+        <v>0.7185185185185186</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7388888888888889</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="20">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.16387943968117</v>
+        <v>0.1592592592592593</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7055555555555556</v>
       </c>
     </row>
     <row r="23">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-0.06324786324786326</v>
+        <v>-0.06324786324786325</v>
       </c>
       <c r="F23" t="n">
         <v>0.3025641025641025</v>
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.2294425546029007</v>
+        <v>0.2537037037037037</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4</v>
+        <v>0.3944444444444444</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="26">
@@ -1250,7 +1250,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-0.03809523809523808</v>
+        <v>-0.03809523809523809</v>
       </c>
       <c r="F27" t="n">
         <v>0.2761904761904762</v>
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3536007169826204</v>
+        <v>0.3518518518518519</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4944444444444445</v>
+        <v>0.4833333333333333</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8555555555555555</v>
+        <v>0.8444444444444444</v>
       </c>
     </row>
     <row r="29">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.05268424026441329</v>
+        <v>0.06296296296296297</v>
       </c>
       <c r="F31" t="n">
         <v>0.3722222222222222</v>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.003418803418803441</v>
+        <v>-0.003418803418803427</v>
       </c>
       <c r="F32" t="n">
         <v>0.2512820512820513</v>
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.4494198765043753</v>
+        <v>0.4425925925925926</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.5055555555555555</v>
       </c>
       <c r="G34" t="n">
-        <v>0.7833333333333333</v>
+        <v>0.7611111111111111</v>
       </c>
     </row>
     <row r="35">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.09592214624283837</v>
+        <v>-0.07777777777777779</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6277777777777778</v>
+        <v>0.6222222222222222</v>
       </c>
     </row>
     <row r="38">
@@ -1653,13 +1653,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5063690455526791</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9277777777777778</v>
+        <v>0.9055555555555556</v>
       </c>
     </row>
     <row r="41">
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7097826875085705</v>
+        <v>0.7259259259259259</v>
       </c>
       <c r="F43" t="n">
         <v>0.7555555555555555</v>
       </c>
       <c r="G43" t="n">
-        <v>0.95</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.7760752041217793</v>
+        <v>0.7814814814814814</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.7722222222222223</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.9722222222222222</v>
       </c>
     </row>
     <row r="47">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.7233909638573659</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="F49" t="n">
         <v>0.7388888888888889</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.5558078204724922</v>
+        <v>0.5851851851851851</v>
       </c>
       <c r="F52" t="n">
-        <v>0.65</v>
+        <v>0.6777777777777778</v>
       </c>
       <c r="G52" t="n">
         <v>0.9111111111111111</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.5765523408963206</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.6555555555555556</v>
       </c>
       <c r="G55" t="n">
         <v>0.9166666666666666</v>
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.2301719562943787</v>
+        <v>0.2407407407407408</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5111111111111111</v>
+        <v>0.4944444444444445</v>
       </c>
       <c r="G58" t="n">
-        <v>0.7444444444444445</v>
+        <v>0.7111111111111111</v>
       </c>
     </row>
     <row r="59">
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.6579308356567186</v>
+        <v>0.6537037037037037</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.6611111111111111</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
   </sheetData>
